--- a/FYP/Matrices/Refined Research Gap Analysis Matrix v5.xlsx
+++ b/FYP/Matrices/Refined Research Gap Analysis Matrix v5.xlsx
@@ -183,7 +183,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -257,6 +257,15 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1325,23 +1334,23 @@
       </c>
     </row>
     <row r="3" ht="330" customHeight="1">
-      <c r="A3" s="19" t="inlineStr">
+      <c r="A3" s="23" t="inlineStr">
         <is>
           <t>Sub-gap 1
 (Former G1)</t>
         </is>
       </c>
-      <c r="B3" s="20" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>NARROWED IN V5. No reviewed work calibrates a nonlinear, depth-conditioned execution-cost function to a thin frontier order book, nor sweeps participation rate to establish the shape of that cost curve where a single order is a material fraction of resting depth; and no portfolio-allocation system embeds such a cost function inside its allocation objective rather than deducting a flat rate after the fact. This is a calibration-and-integration gap, not a modelling-form gap, and the change is deliberate.</t>
         </is>
       </c>
-      <c r="C3" s="20" t="inlineStr">
+      <c r="C3" s="16" t="inlineStr">
         <is>
           <t>Method-Integration + Domain</t>
         </is>
       </c>
-      <c r="D3" s="20" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
         <is>
           <t>THE GENERIC CLAIM IS DEAD AND MUST NOT BE WRITTEN AGAIN. Two papers implement size-dependent execution cost directly. Chen et al. (ICAIF '22) build a queue-reactive LOB simulator where impact is fully endogenous, an order consumes queue, brings a level toward depletion and raises the probability of an adverse mid-price move, and they quantify the cost of ignoring it at 3.04 bps on seven liquid US names. Wang, Gao and Li (Finance and Stochastics 2026) implement Almgren-Chriss explicitly with linear permanent and temporary impact, solve it in closed form, and evaluate inside a LOBSTER historical-order-flow simulator with permanent book contamination. The allocation literature still leaves the assumption intact, Moallemi and Wang assume the order infinitesimal, Guo et al. use one scalar for all assets and sizes, HLOB has no cost model, and the RL survey confirms fixed costs and assumed execution certainty as the field convention with the one modelled form proportional to position change rather than to order size against depth. But that silence is now evidence of a division of labour between the execution and allocation literatures, not of an absence in the field.</t>
         </is>
@@ -1351,54 +1360,56 @@
           <t>Wang, Gao and Li IS the 2026 Almgren-Chriss market-impact work the supervisor cited and v4 carried as unverified, so open item 2 is closed and the supervisor's prediction was correct. Chen et al. is the queue-reactive equivalent. Four things survive them, and the notes state all four independently. (1) NONLINEARITY: every impact model in the set is linear or mechanistic-but-unswept, neither tests a square-root or concave form, and Potters-Bouchaud logarithmic impact appears once in the whole corpus as a future-work line. (2) NO ORDER-SIZE SWEEP ANYWHERE, and both execution notes say it in nearly the same words, Chen et al. running everything at one inventory and horizon and Wang et al. everything at 10% of ADTV, so the shape of the cost curve in order size is empirically untested across the entire set. (3) THIN-MARKET CALIBRATION: not one of the five calibrates to a market where a single order is a visible fraction of resting depth; universes are NASDAQ, IEX and LOBSTER large caps trading 2 to 115 million shares a day. (4) THE PASSIVE SIDE: all three execution papers are market-orders-only, no spread capture, no queue position, no partial fills, no cancellation, no fees. Guo et al. turns from foil into asset here, its transaction remainder factor with constant bounds is the container that lets a cost term stay inside a convex objective rather than sitting outside as a post-hoc deduction, and substituting a state-dependent cost into it is the constructive move.</t>
         </is>
       </c>
-      <c r="F3" s="20" t="inlineStr">
+      <c r="F3" s="16" t="inlineStr">
         <is>
           <t>Unexpected illiquidity shocks depress contemporaneous CSE returns at -0.084 to -0.097, small caps more than large. The amplification argument is now explicit and is the load-bearing sentence: if ignoring impact costs about 3 bps on names trading two to a hundred and fifteen million shares a day, then on a counter where a single order is a visible fraction of resting depth the same neglect is not a small correction to a backtest, it is capable of reversing the sign of a reported edge. That is an argument by amplification rather than a calibrated result, and it should be stated as such.</t>
         </is>
       </c>
-      <c r="G3" s="20" t="inlineStr">
+      <c r="G3" s="16" t="inlineStr">
         <is>
           <t>Technical: a nonlinear, depth-conditioned cost function calibrated to a thin frontier book and embedded inside the allocation objective rather than deducted afterwards. Domain: a participation-rate sweep establishing the shape of the cost curve on a market where order size is material relative to depth, which is the cleanest remaining claim in the set and which no reviewed paper provides for any market.</t>
         </is>
       </c>
-      <c r="H3" s="20" t="inlineStr">
+      <c r="H3" s="16" t="inlineStr">
         <is>
           <t>Substitute a state-dependent cost into Guo et al.'s transaction remainder factor so it stays inside the convex objective. Sweep participation rate rather than fixing it. Prefer a LEARNED friction component over naive calibrate-then-plug-in, on Wang et al.'s own evidence that estimation error in the impact parameters is amplified through the closed-form control, their statistical calibration turning in -905.742 on AAPL at high risk aversion against the learned variant's +102.285, and on CSE data the estimation error would be strictly worse. Run the tick-size classification on CSE counters first, since it needs only best bid, best ask and the tick schedule, and if liquid CSE counters come out small-tick the microstructural route is ruled out at near-zero cost and the friction work is daily-bar-based by necessity rather than preference.</t>
         </is>
       </c>
-      <c r="I3" s="20" t="inlineStr">
-        <is>
-          <t>Per-counter CSE daily price and turnover for the volume profile and the Amihud measure. The data ladder is now explicit: level-III message data for the full queue-reactive route and almost certainly out of reach; multi-level depth snapshots for a weaker version; top-of-book only for the tick classification, which is decisive and nearly free and runs first; intraday trade-and-quote without depth for the five-scalar policy route, which is fittable on a short archive where a learned agent is not; and daily bars only for the fallback, turnover, traded value, zero-return frequency and Amihud-style measures.</t>
-        </is>
-      </c>
-      <c r="J3" s="20" t="inlineStr">
+      <c r="I3" s="16" t="inlineStr">
+        <is>
+          <t>Per-counter CSE daily price and turnover for the volume profile and the Amihud measure. The data ladder is now explicit: level-III message data for the full queue-reactive route and almost certainly out of reach; multi-level depth snapshots for a weaker version; top-of-book only for the tick classification, which is decisive and nearly free and runs first; intraday trade-and-quote without depth for the five-scalar policy route, which is fittable on a short archive where a learned agent is not; and daily bars only for the fallback, turnover, traded value, zero-return frequency and Amihud-style measures.
+AMENDED 11 OCTOBER 2026: the bottom rung of that ladder is where this now sits, and it has no spread measurement on it. The EDGE route that would have put a measured effective spread on the daily-bars rung is demoted to last resort and is not assumed available. This changes what the CSE request is for: bid/ask and depth are no longer a validation extra for an estimator already built, they are the only route to a measured spread, which moves them to the top of the request rather than the middle.</t>
+        </is>
+      </c>
+      <c r="J3" s="16" t="inlineStr">
         <is>
           <t>(a) Zero-cost execution. (b) Flat 2 bps. (c) FreQuant's solved fee fixed point with no impact term. (d) Naive full-size execution at close. (e) NEW, Almgren-Chriss at a fixed participation rate, which is now the strongest published treatment and therefore the baseline that actually matters. (f) NEW, the 19-strategy training-free OLPS family plus First All / Last All / TWAP / VWAP.</t>
         </is>
       </c>
-      <c r="K3" s="20" t="inlineStr">
+      <c r="K3" s="16" t="inlineStr">
         <is>
           <t>The framework under all cost regimes, plus the participation-rate sweep that is missing from the whole literature. TWO EXPERIMENTS ARE INDEPENDENT OF THE CSE DATA BLOCKER and both should run while the data request is outstanding: sweeping the cost parameter from 5 bps to north of 100 bps on Guo et al.'s own four datasets, which establishes where the crossover against simpler baselines sits and is directly the argument for why a frontier market needs different machinery; and the tick-size classification on CSE counters from top-of-book alone. Report the half-spread unit, average transaction cost in bps against the decision price, risk-adjusted PnL relative to TWAP, and round-trip practicability against action count, since the first two are pure cost measures indifferent between a reliable schedule and a volatile one.</t>
         </is>
       </c>
-      <c r="L3" s="20" t="inlineStr">
+      <c r="L3" s="16" t="inlineStr">
         <is>
           <t>High for the daily-turnover version and for both blocker-independent experiments. Low for anything needing level-III messages or queue intensities, which the notes judge almost certainly out of reach. The evaluation layer and A_L are gated on exactly the same data, so whatever cannot be observed cannot be simulated either, and they should be treated as one workstream and one data request rather than two.</t>
         </is>
       </c>
-      <c r="M3" s="20" t="inlineStr">
-        <is>
-          <t>The novelty has genuinely narrowed and the rating moves with it rather than being defended at its old level. There is still no ground-truth execution data to validate a CSE simulator against, so simulated slippage is not measured slippage and must be presented that way. The tick-size classification may return small-tick, which would close the microstructural route entirely. And a reviewer who knows the execution literature will ask why the impact model is not simply Almgren-Chriss with CSE parameters, so the nonlinearity and the in-objective embedding have to be the argued contribution rather than the calibration alone.</t>
-        </is>
-      </c>
-      <c r="N3" s="21" t="inlineStr">
+      <c r="M3" s="16" t="inlineStr">
+        <is>
+          <t>The novelty has genuinely narrowed and the rating moves with it rather than being defended at its old level. There is still no ground-truth execution data to validate a CSE simulator against, so simulated slippage is not measured slippage and must be presented that way. The tick-size classification may return small-tick, which would close the microstructural route entirely. And a reviewer who knows the execution literature will ask why the impact model is not simply Almgren-Chriss with CSE parameters, so the nonlinearity and the in-objective embedding have to be the argued contribution rather than the calibration alone.
+ADDED 11 OCTOBER 2026 - SUB-GAP 1 NOW CARRIES TWO CAVEATS AND THEY MUST BE STATED TOGETHER. (1) Smart Trading Rule (Journal of Financial Data Science 8(2), 2026) was identified, judged potentially overlapping on the modular transaction-cost layer, and could not be obtained because it is paywalled. Its contents are unknown to me, so this sub-gap is not presented as though the literature had been fully swept. (2) THE MEASUREMENT HALF IS OPEN AGAIN. P54, the EDGE estimator of effective spread from daily OHLC, was the route that would have substituted for the CSE's missing quote data, and on 11 October it was demoted to last resort because it is unvalidated on thin and frontier markets - no emerging or frontier market appears anywhere in that paper, its crypto section has no quote benchmark at all, and its own numbers put it at its weakest exactly where the CSE sits. With no CSE quote data to validate against, an EDGE spread here could not be falsified even in principle. So the cost term rests on proxies for illiquidity - Amihud, turnover, zero-return frequency and the high-low range - rather than on any measurement of what a trade actually pays. That is a weaker evidential base than v5 recorded and the write-up should say so rather than leave it to be found. The defensible form is that the cost function is calibrated on proxies because no validated spread measurement exists for this market, and that validating it is what the CSE data request is for.</t>
+        </is>
+      </c>
+      <c r="N3" s="27" t="inlineStr">
         <is>
           <t>3 / 5</t>
         </is>
       </c>
-      <c r="O3" s="18" t="inlineStr">
-        <is>
-          <t>RETAIN, NARROWED - generic claim withdrawn, calibration and in-objective embedding retained</t>
+      <c r="O3" s="23" t="inlineStr">
+        <is>
+          <t>RETAIN, NARROWED - generic claim withdrawn, calibration and in-objective embedding retained  |  11 Oct 2026: unchanged in substance, but state it with BOTH caveats - the unobtainable Smart Trading Rule and the demoted EDGE proxy route.</t>
         </is>
       </c>
     </row>
@@ -2300,7 +2311,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A20"/>
+  <dimension ref="A1:A23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="124" customWidth="1" min="1" max="1"/>
@@ -2422,6 +2433,20 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="28" t="inlineStr">
+        <is>
+          <t>Amendment, 11 October 2026 - Sub-gap 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="150" customHeight="1">
+      <c r="A23" s="29" t="inlineStr">
+        <is>
+          <t>Sub-gap 1 now carries two caveats and they belong in the write-up together. First, Smart Trading Rule (JFDS 8(2), 2026) was identified, judged potentially overlapping, and could not be obtained - it is paywalled, its contents are unknown, and the sub-gap is not presented as a fully swept literature. Second, P54 EDGE has been demoted to last resort because it is unvalidated on thin and frontier markets and the CSE has no quote data to validate it against, so the measurement half of the sub-gap is open again and the cost term rests on proxies - Amihud, turnover, zero-return frequency and the high-low range. The practical effect is that the CSE request for bid/ask and depth is now the only route to a measured spread rather than a validation extra, and it should be pressed accordingly. The Sub-gap 1 row is marked amber. Full reasoning is in the Literature Survey Matrix Read Me and in the vault note for the EDGE paper.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
